--- a/总结.xlsx
+++ b/总结.xlsx
@@ -1,26 +1,219 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\l\Desktop\DEIMv2-main\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B6FA277-74AD-435A-8FDA-37A52F587913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="57">
+  <si>
+    <t>experiment</t>
+  </si>
+  <si>
+    <t>water_features</t>
+  </si>
+  <si>
+    <t>water_self_attn</t>
+  </si>
+  <si>
+    <t>query_water_cross_attn</t>
+  </si>
+  <si>
+    <t>learnable_gate</t>
+  </si>
+  <si>
+    <t>Precision</t>
+  </si>
+  <si>
+    <t>Recall</t>
+  </si>
+  <si>
+    <t>F1</t>
+  </si>
+  <si>
+    <t>mAP50</t>
+  </si>
+  <si>
+    <t>mAP50_95</t>
+  </si>
+  <si>
+    <t>AP75</t>
+  </si>
+  <si>
+    <t>Params_M</t>
+  </si>
+  <si>
+    <t>GFLOPs</t>
+  </si>
+  <si>
+    <t>M0_visual</t>
+  </si>
+  <si>
+    <t>0.8571428571428571</t>
+  </si>
+  <si>
+    <t>0.8415374241402562</t>
+  </si>
+  <si>
+    <t>0.8876775751246994</t>
+  </si>
+  <si>
+    <t>0.6749161133856686</t>
+  </si>
+  <si>
+    <t>0.7577290407099994</t>
+  </si>
+  <si>
+    <t>M1_QCA</t>
+  </si>
+  <si>
+    <t>temperature+do+ph</t>
+  </si>
+  <si>
+    <t>0.8668918918918919</t>
+  </si>
+  <si>
+    <t>0.8651382333108564</t>
+  </si>
+  <si>
+    <t>0.8660141748228147</t>
+  </si>
+  <si>
+    <t>0.6831630576455255</t>
+  </si>
+  <si>
+    <t>0.7694600760852467</t>
+  </si>
+  <si>
+    <t>M2_SA_QCA</t>
+  </si>
+  <si>
+    <t>0.8818181818181818</t>
+  </si>
+  <si>
+    <t>0.8503034389750506</t>
+  </si>
+  <si>
+    <t>0.8657741160315825</t>
+  </si>
+  <si>
+    <t>0.6905934097032302</t>
+  </si>
+  <si>
+    <t>0.7743501038509741</t>
+  </si>
+  <si>
+    <t>M3_QCA_Gate</t>
+  </si>
+  <si>
+    <t>0.8823114869626497</t>
+  </si>
+  <si>
+    <t>0.8442346594740391</t>
+  </si>
+  <si>
+    <t>0.8628532046864231</t>
+  </si>
+  <si>
+    <t>0.8934240163861548</t>
+  </si>
+  <si>
+    <t>0.6806223249505164</t>
+  </si>
+  <si>
+    <t>0.7643915414646978</t>
+  </si>
+  <si>
+    <t>M4_full</t>
+  </si>
+  <si>
+    <t>0.8782006920415225</t>
+  </si>
+  <si>
+    <t>0.8556979096426163</t>
+  </si>
+  <si>
+    <t>0.8668032786885245</t>
+  </si>
+  <si>
+    <t>0.6893372289795596</t>
+  </si>
+  <si>
+    <t>0.7716551538436156</t>
+  </si>
+  <si>
+    <t>V0_visual</t>
+  </si>
+  <si>
+    <t>V1_T_DO_pH_Tur</t>
+  </si>
+  <si>
+    <t>temperature+do+ph+turbidity</t>
+  </si>
+  <si>
+    <t>V2_T_DO_pH</t>
+  </si>
+  <si>
+    <t>V3_DO_pH</t>
+  </si>
+  <si>
+    <t>do+ph</t>
+  </si>
+  <si>
+    <t>V4_T_pH</t>
+  </si>
+  <si>
+    <t>temperature+ph</t>
+  </si>
+  <si>
+    <t>V5_T_DO</t>
+  </si>
+  <si>
+    <t>temperature+do</t>
+  </si>
+  <si>
+    <t>V6_DO</t>
+  </si>
+  <si>
+    <t>do</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -28,13 +221,26 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -49,11 +255,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" quotePrefix="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -330,10 +549,567 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:M14"/>
+  <sheetFormatPr defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
+      <c r="F2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="1">
+        <v>0.84926845865940803</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="L2" s="1">
+        <v>1.495547</v>
+      </c>
+      <c r="M2" s="1">
+        <v>5.1668614560000004</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E3" s="1"/>
+      <c r="F3" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="I3" s="1">
+        <v>0.89613647065646296</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="L3" s="1">
+        <v>1.9235629999999999</v>
+      </c>
+      <c r="M3" s="1">
+        <v>5.3194164480000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E4" s="1"/>
+      <c r="F4" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="1">
+        <v>0.89878232752480602</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="L4" s="1">
+        <v>1.9988300000000001</v>
+      </c>
+      <c r="M4" s="1">
+        <v>5.3198691839999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="1"/>
+      <c r="D5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="L5" s="1">
+        <v>1.9235690000000001</v>
+      </c>
+      <c r="M5" s="1">
+        <v>5.3194164480000001</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6" s="1" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I6" s="4">
+        <v>0.90117788692155798</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="L6" s="1">
+        <v>1.9988360000000001</v>
+      </c>
+      <c r="M6" s="1">
+        <v>5.3198691839999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" t="s">
+        <v>4</v>
+      </c>
+      <c r="F7" t="s">
+        <v>5</v>
+      </c>
+      <c r="G7" t="s">
+        <v>6</v>
+      </c>
+      <c r="H7" t="s">
+        <v>7</v>
+      </c>
+      <c r="I7" t="s">
+        <v>8</v>
+      </c>
+      <c r="J7" t="s">
+        <v>9</v>
+      </c>
+      <c r="K7" t="s">
+        <v>10</v>
+      </c>
+      <c r="L7" t="s">
+        <v>11</v>
+      </c>
+      <c r="M7" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" t="b">
+        <v>0</v>
+      </c>
+      <c r="D8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" t="b">
+        <v>0</v>
+      </c>
+      <c r="F8">
+        <v>0.85763411279229695</v>
+      </c>
+      <c r="G8">
+        <v>0.84086311530681002</v>
+      </c>
+      <c r="H8">
+        <v>0.84916581545795</v>
+      </c>
+      <c r="I8">
+        <v>0.883214603510593</v>
+      </c>
+      <c r="J8">
+        <v>0.67365954310890397</v>
+      </c>
+      <c r="K8">
+        <v>0.76357269488998503</v>
+      </c>
+      <c r="L8">
+        <v>1.495547</v>
+      </c>
+      <c r="M8">
+        <v>5.1668614560000004</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>46</v>
+      </c>
+      <c r="B9" t="s">
+        <v>47</v>
+      </c>
+      <c r="C9" t="b">
+        <v>1</v>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9" t="b">
+        <v>1</v>
+      </c>
+      <c r="F9">
+        <v>0.87649122807017499</v>
+      </c>
+      <c r="G9">
+        <v>0.84221173299999996</v>
+      </c>
+      <c r="H9">
+        <v>0.859009629</v>
+      </c>
+      <c r="I9">
+        <v>0.89451304778276897</v>
+      </c>
+      <c r="J9">
+        <v>0.68332525932988897</v>
+      </c>
+      <c r="K9" s="5">
+        <v>0.77003997035302996</v>
+      </c>
+      <c r="L9">
+        <v>1.999028</v>
+      </c>
+      <c r="M9">
+        <v>5.3203852319999996</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>48</v>
+      </c>
+      <c r="B10" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" t="b">
+        <v>1</v>
+      </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10" t="b">
+        <v>1</v>
+      </c>
+      <c r="F10" s="5">
+        <v>0.89575844716031605</v>
+      </c>
+      <c r="G10">
+        <v>0.84018880647336402</v>
+      </c>
+      <c r="H10" s="5">
+        <v>0.86708420320111301</v>
+      </c>
+      <c r="I10">
+        <v>0.89757149884735998</v>
+      </c>
+      <c r="J10" s="5">
+        <v>0.683685119267883</v>
+      </c>
+      <c r="K10">
+        <v>0.76920897171444003</v>
+      </c>
+      <c r="L10">
+        <v>1.9988360000000001</v>
+      </c>
+      <c r="M10">
+        <v>5.3198691839999999</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" t="b">
+        <v>1</v>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>0.89427950760318597</v>
+      </c>
+      <c r="G11">
+        <v>0.83277140930546101</v>
+      </c>
+      <c r="H11">
+        <v>0.86243016759776503</v>
+      </c>
+      <c r="I11" s="5">
+        <v>0.89964918683456496</v>
+      </c>
+      <c r="J11">
+        <v>0.68127417685504099</v>
+      </c>
+      <c r="K11">
+        <v>0.76897994866341002</v>
+      </c>
+      <c r="L11">
+        <v>1.9986440000000001</v>
+      </c>
+      <c r="M11">
+        <v>5.3193546720000002</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>51</v>
+      </c>
+      <c r="B12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C12" t="b">
+        <v>1</v>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12" t="b">
+        <v>1</v>
+      </c>
+      <c r="F12">
+        <v>0.83921568627450904</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0.86581254214430203</v>
+      </c>
+      <c r="H12">
+        <v>0.85230667109193503</v>
+      </c>
+      <c r="I12">
+        <v>0.89163607440518</v>
+      </c>
+      <c r="J12">
+        <v>0.67433797600000001</v>
+      </c>
+      <c r="K12">
+        <v>0.760691368623578</v>
+      </c>
+      <c r="L12">
+        <v>1.9986440000000001</v>
+      </c>
+      <c r="M12">
+        <v>5.3193546720000002</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" t="b">
+        <v>1</v>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
+      </c>
+      <c r="E13" t="b">
+        <v>1</v>
+      </c>
+      <c r="F13">
+        <v>0.85399999999999998</v>
+      </c>
+      <c r="G13">
+        <v>0.86378961600000004</v>
+      </c>
+      <c r="H13">
+        <v>0.85886691250419001</v>
+      </c>
+      <c r="I13">
+        <v>0.89006509489227603</v>
+      </c>
+      <c r="J13">
+        <v>0.67553030678780901</v>
+      </c>
+      <c r="K13">
+        <v>0.76132902997759799</v>
+      </c>
+      <c r="L13">
+        <v>1.9986440000000001</v>
+      </c>
+      <c r="M13">
+        <v>5.3193546720000002</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C14" t="b">
+        <v>1</v>
+      </c>
+      <c r="D14" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>0.88070175438596399</v>
+      </c>
+      <c r="G14">
+        <v>0.84625758597437595</v>
+      </c>
+      <c r="H14">
+        <v>0.863136176066024</v>
+      </c>
+      <c r="I14">
+        <v>0.89665422533868999</v>
+      </c>
+      <c r="J14">
+        <v>0.67853175499999996</v>
+      </c>
+      <c r="K14">
+        <v>0.76537818573097804</v>
+      </c>
+      <c r="L14">
+        <v>1.9984519999999999</v>
+      </c>
+      <c r="M14">
+        <v>5.3188416959999998</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>